--- a/src/scripts/random_eval_2.xlsx
+++ b/src/scripts/random_eval_2.xlsx
@@ -28,14 +28,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-    </font>
-    <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="10"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -57,15 +57,18 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -463,64 +466,25 @@
             <t xml:space="preserve">0. </t>
           </r>
           <r>
-            <t>Review the JudgeSystem and JudgeUser prompts to understand the criteria used during realism evaluation.</t>
+            <t>Review the following prompts to understand the criteria used during realism evaluation.</t>
           </r>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t xml:space="preserve">1. </t>
-          </r>
-          <r>
-            <t>Open and review the instance from the hyperlink in the first column.</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t>System Judge: https://a-coman.github.io/llm-viewer/gpt_4o/bank/gen1/?view=system-judge-prompt</t>
           </r>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t xml:space="preserve">2. </t>
-          </r>
-          <r>
-            <t xml:space="preserve">In your corresponding reviewer column, write </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>'R'</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> (realistic), </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>'U'</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> (unrealistic), or </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>'D'</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> (doubtful).</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t>User Judge: https://a-coman.github.io/llm-viewer/gpt_4o/bank/gen1/?view=user-judge-prompt</t>
           </r>
         </is>
       </c>
@@ -532,16 +496,10 @@
             <rPr>
               <b val="1"/>
             </rPr>
-            <t xml:space="preserve">3. </t>
-          </r>
-          <r>
-            <t xml:space="preserve">Add a short explanation only for U or D, for example: </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>'U: It is implausible to make an omelet without eggs.'</t>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <t>Open and review the instance from the hyperlink in the first column.</t>
           </r>
         </is>
       </c>
@@ -550,6 +508,69 @@
       <c r="A6" s="1" t="inlineStr">
         <is>
           <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">2. </t>
+          </r>
+          <r>
+            <t xml:space="preserve">In your corresponding reviewer column, write </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>'R'</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (realistic), </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>'U'</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (unrealistic), or </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>'D'</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (doubtful).</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">3. </t>
+          </r>
+          <r>
+            <t xml:space="preserve">Add a short explanation only for U or D, for example: </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>'U: It is implausible to make an omelet without eggs.'</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <r>
             <t xml:space="preserve">Another valid example: </t>
           </r>
           <r>
@@ -561,40 +582,8 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Instance Id</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Lola</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Dominik</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Manuel</t>
-        </is>
-      </c>
-    </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / cot / videoclub / gen5 / baseline</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -602,17 +591,29 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / football / gen2 / edge</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>Instance Id</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Lola</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Dominik</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / cot / hotelmanagement / gen6 / invalid</t>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / cot / videoclub / gen5 / baseline</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -620,9 +621,9 @@
       <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / simple / myexpenses / gen30</t>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / cot / football / gen2 / edge</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -630,9 +631,9 @@
       <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / cot / statemachine / gen1 / invalid</t>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / cot / hotelmanagement / gen6 / invalid</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -640,9 +641,9 @@
       <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / simple / hotelmanagement / gen7</t>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / simple / myexpenses / gen30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -650,9 +651,9 @@
       <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / simple / videoclub / gen9</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / cot / statemachine / gen1 / invalid</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -660,9 +661,9 @@
       <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / simple / bank / gen2</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / simple / hotelmanagement / gen7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -670,9 +671,9 @@
       <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / simple / pickupnet / gen23</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / simple / videoclub / gen9</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -680,9 +681,9 @@
       <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / cot / videoclub / gen6 / complex</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / simple / bank / gen2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -690,9 +691,9 @@
       <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / simple / addressbook / gen21</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / simple / pickupnet / gen23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -700,9 +701,9 @@
       <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / simple / myexpenses / gen5</t>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / cot / videoclub / gen6 / complex</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -710,9 +711,9 @@
       <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / cot / myexpenses / gen1 / boundary</t>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / simple / addressbook / gen21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -720,9 +721,9 @@
       <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / cot / football / gen2 / invalid</t>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / simple / myexpenses / gen5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -730,9 +731,9 @@
       <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / simple / myexpenses / gen27</t>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / cot / myexpenses / gen1 / boundary</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -740,9 +741,9 @@
       <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / simple / statemachine / gen25</t>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / cot / football / gen2 / invalid</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -750,9 +751,9 @@
       <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / cot / football / gen5 / baseline</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / simple / myexpenses / gen27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -760,9 +761,9 @@
       <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / cot / addressbook / gen2 / complex</t>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / simple / statemachine / gen25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -770,9 +771,9 @@
       <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / simple / videoclub / gen1</t>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / cot / football / gen5 / baseline</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -780,9 +781,9 @@
       <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / simple / myexpenses / gen3</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / cot / addressbook / gen2 / complex</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -790,9 +791,9 @@
       <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / cot / restaurant / gen3 / complex</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / simple / videoclub / gen1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -800,9 +801,9 @@
       <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / cot / videoclub / gen2 / boundary</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / simple / myexpenses / gen3</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -810,9 +811,9 @@
       <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / simple / pickupnet / gen10</t>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / cot / restaurant / gen3 / complex</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -820,27 +821,49 @@
       <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / cot / football / gen6 / baseline</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / cot / videoclub / gen2 / boundary</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / simple / pickupnet / gen10</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / cot / football / gen6 / baseline</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A8:D8"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A7:D7"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId5"/>
@@ -863,6 +886,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -874,7 +899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -905,64 +930,25 @@
             <t xml:space="preserve">0. </t>
           </r>
           <r>
-            <t>Review the JudgeSystem and JudgeUser prompts to understand the criteria used during realism evaluation.</t>
+            <t>Review the following prompts to understand the criteria used during realism evaluation.</t>
           </r>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t xml:space="preserve">1. </t>
-          </r>
-          <r>
-            <t>Open and review the instance from the hyperlink in the first column.</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t>System Judge: https://a-coman.github.io/llm-viewer/gpt_4o/bank/gen1/?view=system-judge-prompt</t>
           </r>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t xml:space="preserve">2. </t>
-          </r>
-          <r>
-            <t xml:space="preserve">In your corresponding reviewer column, write </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>'R'</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> (realistic), </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>'U'</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> (unrealistic), or </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>'D'</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> (doubtful).</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t>User Judge: https://a-coman.github.io/llm-viewer/gpt_4o/bank/gen1/?view=user-judge-prompt</t>
           </r>
         </is>
       </c>
@@ -974,16 +960,10 @@
             <rPr>
               <b val="1"/>
             </rPr>
-            <t xml:space="preserve">3. </t>
-          </r>
-          <r>
-            <t xml:space="preserve">Add a short explanation only for U or D, for example: </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>'U: It is implausible to make an omelet without eggs.'</t>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <t>Open and review the instance from the hyperlink in the first column.</t>
           </r>
         </is>
       </c>
@@ -992,6 +972,69 @@
       <c r="A6" s="1" t="inlineStr">
         <is>
           <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">2. </t>
+          </r>
+          <r>
+            <t xml:space="preserve">In your corresponding reviewer column, write </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>'R'</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (realistic), </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>'U'</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (unrealistic), or </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>'D'</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (doubtful).</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">3. </t>
+          </r>
+          <r>
+            <t xml:space="preserve">Add a short explanation only for U or D, for example: </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>'U: It is implausible to make an omelet without eggs.'</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <r>
             <t xml:space="preserve">Another valid example: </t>
           </r>
           <r>
@@ -1003,40 +1046,8 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Instance Id</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Lola</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Manuel</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Dominik</t>
-        </is>
-      </c>
-    </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / simple / vehiclerental / gen12</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -1044,17 +1055,29 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / videoclub / gen6 / boundary</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>Instance Id</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Lola</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Dominik</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / simple / hotelmanagement / gen1</t>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / simple / vehiclerental / gen12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -1062,9 +1085,9 @@
       <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / simple / myexpenses / gen16</t>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / cot / videoclub / gen6 / boundary</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -1072,9 +1095,9 @@
       <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / simple / vehiclerental / gen20</t>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / simple / hotelmanagement / gen1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -1082,9 +1105,9 @@
       <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / simple / videoclub / gen18</t>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / simple / myexpenses / gen16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -1092,9 +1115,9 @@
       <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / cot / vehiclerental / gen3 / complex</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / simple / vehiclerental / gen20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -1102,9 +1125,9 @@
       <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / simple / restaurant / gen25</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / simple / videoclub / gen18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -1112,9 +1135,9 @@
       <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / simple / addressbook / gen6</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / cot / vehiclerental / gen3 / complex</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1122,9 +1145,9 @@
       <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / cot / restaurant / gen4 / invalid</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / simple / restaurant / gen25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1132,9 +1155,9 @@
       <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / cot / myexpenses / gen3 / complex</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / simple / addressbook / gen6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1142,9 +1165,9 @@
       <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / simple / statemachine / gen7</t>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / cot / restaurant / gen4 / invalid</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1152,9 +1175,9 @@
       <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / cot / hotelmanagement / gen2 / baseline</t>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / cot / myexpenses / gen3 / complex</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1162,9 +1185,9 @@
       <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / cot / football / gen4 / invalid</t>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / simple / statemachine / gen7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1172,9 +1195,9 @@
       <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / cot / videoclub / gen2 / edge</t>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / cot / hotelmanagement / gen2 / baseline</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1182,9 +1205,9 @@
       <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / simple / bank / gen24</t>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / cot / football / gen4 / invalid</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1192,9 +1215,9 @@
       <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / simple / statemachine / gen20</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / cot / videoclub / gen2 / edge</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1202,9 +1225,9 @@
       <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / simple / statemachine / gen27</t>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / simple / bank / gen24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1212,9 +1235,9 @@
       <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / simple / statemachine / gen18</t>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / simple / statemachine / gen20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1222,9 +1245,9 @@
       <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / simple / videoclub / gen15</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / simple / statemachine / gen27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1232,9 +1255,9 @@
       <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / simple / vehiclerental / gen12</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / simple / statemachine / gen18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1242,9 +1265,9 @@
       <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / simple / addressbook / gen29</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / simple / videoclub / gen15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1252,9 +1275,9 @@
       <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / simple / pickupnet / gen22</t>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / simple / vehiclerental / gen12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1262,27 +1285,49 @@
       <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / cot / statemachine / gen1 / edge</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / simple / addressbook / gen29</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / simple / pickupnet / gen22</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / cot / statemachine / gen1 / edge</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A8:D8"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A7:D7"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId5"/>
@@ -1305,6 +1350,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1316,7 +1363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1347,64 +1394,25 @@
             <t xml:space="preserve">0. </t>
           </r>
           <r>
-            <t>Review the JudgeSystem and JudgeUser prompts to understand the criteria used during realism evaluation.</t>
+            <t>Review the following prompts to understand the criteria used during realism evaluation.</t>
           </r>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t xml:space="preserve">1. </t>
-          </r>
-          <r>
-            <t>Open and review the instance from the hyperlink in the first column.</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t>System Judge: https://a-coman.github.io/llm-viewer/gpt_4o/bank/gen1/?view=system-judge-prompt</t>
           </r>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t xml:space="preserve">2. </t>
-          </r>
-          <r>
-            <t xml:space="preserve">In your corresponding reviewer column, write </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>'R'</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> (realistic), </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>'U'</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> (unrealistic), or </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>'D'</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> (doubtful).</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t>User Judge: https://a-coman.github.io/llm-viewer/gpt_4o/bank/gen1/?view=user-judge-prompt</t>
           </r>
         </is>
       </c>
@@ -1416,16 +1424,10 @@
             <rPr>
               <b val="1"/>
             </rPr>
-            <t xml:space="preserve">3. </t>
-          </r>
-          <r>
-            <t xml:space="preserve">Add a short explanation only for U or D, for example: </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>'U: It is implausible to make an omelet without eggs.'</t>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <t>Open and review the instance from the hyperlink in the first column.</t>
           </r>
         </is>
       </c>
@@ -1434,6 +1436,69 @@
       <c r="A6" s="1" t="inlineStr">
         <is>
           <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">2. </t>
+          </r>
+          <r>
+            <t xml:space="preserve">In your corresponding reviewer column, write </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>'R'</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (realistic), </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>'U'</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (unrealistic), or </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>'D'</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (doubtful).</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">3. </t>
+          </r>
+          <r>
+            <t xml:space="preserve">Add a short explanation only for U or D, for example: </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>'U: It is implausible to make an omelet without eggs.'</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <r>
             <t xml:space="preserve">Another valid example: </t>
           </r>
           <r>
@@ -1445,40 +1510,8 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Instance Id</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Dominik</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Manuel</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Lola</t>
-        </is>
-      </c>
-    </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / cot / statemachine / gen3 / complex</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -1486,17 +1519,29 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / vehiclerental / gen2 / complex</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>Instance Id</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Dominik</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Lola</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / cot / vehiclerental / gen1 / baseline</t>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / cot / statemachine / gen3 / complex</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -1504,9 +1549,9 @@
       <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / cot / vehiclerental / gen3 / invalid</t>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / cot / vehiclerental / gen2 / complex</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -1514,9 +1559,9 @@
       <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / simple / hotelmanagement / gen27</t>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / cot / vehiclerental / gen1 / baseline</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -1524,9 +1569,9 @@
       <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / cot / addressbook / gen6 / edge</t>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / cot / vehiclerental / gen3 / invalid</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -1534,9 +1579,9 @@
       <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / simple / bank / gen5</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / simple / hotelmanagement / gen27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -1544,9 +1589,9 @@
       <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / cot / addressbook / gen2 / boundary</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / cot / addressbook / gen6 / edge</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -1554,9 +1599,9 @@
       <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / cot / hotelmanagement / gen3 / edge</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / simple / bank / gen5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1564,9 +1609,9 @@
       <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / cot / myexpenses / gen6 / baseline</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / cot / addressbook / gen2 / boundary</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1574,9 +1619,9 @@
       <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / simple / bank / gen27</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / cot / hotelmanagement / gen3 / edge</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1584,9 +1629,9 @@
       <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / simple / hotelmanagement / gen27</t>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / cot / myexpenses / gen6 / baseline</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1594,9 +1639,9 @@
       <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / simple / statemachine / gen3</t>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / simple / bank / gen27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1604,9 +1649,9 @@
       <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / cot / bank / gen6 / invalid</t>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / simple / hotelmanagement / gen27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1614,9 +1659,9 @@
       <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / cot / pickupnet / gen2 / edge</t>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / simple / statemachine / gen3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1624,9 +1669,9 @@
       <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / cot / bank / gen3 / invalid</t>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / cot / bank / gen6 / invalid</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1634,9 +1679,9 @@
       <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / cot / pickupnet / gen2 / edge</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / cot / pickupnet / gen2 / edge</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1644,9 +1689,9 @@
       <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / simple / vehiclerental / gen25</t>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / cot / bank / gen3 / invalid</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1654,9 +1699,9 @@
       <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / cot / myexpenses / gen1 / invalid</t>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / cot / pickupnet / gen2 / edge</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1664,9 +1709,9 @@
       <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / simple / pickupnet / gen26</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / simple / vehiclerental / gen25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1674,9 +1719,9 @@
       <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / cot / football / gen6 / invalid</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / cot / myexpenses / gen1 / invalid</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1684,9 +1729,9 @@
       <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / simple / addressbook / gen8</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / simple / pickupnet / gen26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1694,9 +1739,9 @@
       <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / cot / pickupnet / gen6 / edge</t>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / cot / football / gen6 / invalid</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1704,27 +1749,49 @@
       <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>gpt_4o / cot / myexpenses / gen3 / boundary</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / simple / addressbook / gen8</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>gpt_5_2 / cot / pickupnet / gen6 / edge</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>gpt_4o / cot / myexpenses / gen3 / boundary</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A8:D8"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A7:D7"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId5"/>
@@ -1747,6 +1814,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/scripts/random_eval_2.xlsx
+++ b/src/scripts/random_eval_2.xlsx
@@ -499,7 +499,7 @@
             <t xml:space="preserve">1. </t>
           </r>
           <r>
-            <t>Open and review the instance from the hyperlink in the first column.</t>
+            <t>Understand the model (diagram/code) and review the instance (diagram/code) from the hyperlink in the first column.</t>
           </r>
         </is>
       </c>
@@ -514,7 +514,7 @@
             <t xml:space="preserve">2. </t>
           </r>
           <r>
-            <t xml:space="preserve">In your corresponding reviewer column, write </t>
+            <t xml:space="preserve">In your corresponding reviewer excel, page and column, write </t>
           </r>
           <r>
             <rPr>
@@ -963,7 +963,7 @@
             <t xml:space="preserve">1. </t>
           </r>
           <r>
-            <t>Open and review the instance from the hyperlink in the first column.</t>
+            <t>Understand the model (diagram/code) and review the instance (diagram/code) from the hyperlink in the first column.</t>
           </r>
         </is>
       </c>
@@ -978,7 +978,7 @@
             <t xml:space="preserve">2. </t>
           </r>
           <r>
-            <t xml:space="preserve">In your corresponding reviewer column, write </t>
+            <t xml:space="preserve">In your corresponding reviewer excel, page and column, write </t>
           </r>
           <r>
             <rPr>
@@ -1427,7 +1427,7 @@
             <t xml:space="preserve">1. </t>
           </r>
           <r>
-            <t>Open and review the instance from the hyperlink in the first column.</t>
+            <t>Understand the model (diagram/code) and review the instance (diagram/code) from the hyperlink in the first column.</t>
           </r>
         </is>
       </c>
@@ -1442,7 +1442,7 @@
             <t xml:space="preserve">2. </t>
           </r>
           <r>
-            <t xml:space="preserve">In your corresponding reviewer column, write </t>
+            <t xml:space="preserve">In your corresponding reviewer excel, page and column, write </t>
           </r>
           <r>
             <rPr>

--- a/src/scripts/random_eval_2.xlsx
+++ b/src/scripts/random_eval_2.xlsx
@@ -466,7 +466,7 @@
             <t xml:space="preserve">0. </t>
           </r>
           <r>
-            <t>Review the following prompts to understand the criteria used during realism evaluation.</t>
+            <t>Review the judge prompts to understand the criteria used during realism evaluation.</t>
           </r>
         </is>
       </c>
@@ -475,7 +475,7 @@
       <c r="A3" s="2" t="inlineStr">
         <is>
           <r>
-            <t>System Judge: https://a-coman.github.io/llm-viewer/gpt_4o/bank/gen1/?view=system-judge-prompt</t>
+            <t>Judge System Prompt: https://a-coman.github.io/llm-viewer/gpt_4o/bank/gen1/?view=system-judge-prompt</t>
           </r>
         </is>
       </c>
@@ -484,7 +484,7 @@
       <c r="A4" s="2" t="inlineStr">
         <is>
           <r>
-            <t>User Judge: https://a-coman.github.io/llm-viewer/gpt_4o/bank/gen1/?view=user-judge-prompt</t>
+            <t>Judge User Prompt: https://a-coman.github.io/llm-viewer/gpt_4o/bank/gen1/?view=user-judge-prompt</t>
           </r>
         </is>
       </c>
@@ -613,7 +613,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / videoclub / gen5 / baseline</t>
+          <t>gpt_5_2 / cot / videoclub / gen6 / invalid</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -623,7 +623,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / football / gen2 / edge</t>
+          <t>gpt_4o / cot / addressbook / gen6 / invalid</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -633,7 +633,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / hotelmanagement / gen6 / invalid</t>
+          <t>gpt_5_2 / cot / hotelmanagement / gen4 / edge</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -643,7 +643,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / myexpenses / gen30</t>
+          <t>gpt_5_2 / simple / myexpenses / gen20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -653,7 +653,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / statemachine / gen1 / invalid</t>
+          <t>gpt_4o / cot / statemachine / gen6 / invalid</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -663,7 +663,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / hotelmanagement / gen7</t>
+          <t>gpt_5_2 / simple / pickupnet / gen24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -673,7 +673,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / videoclub / gen9</t>
+          <t>gpt_4o / simple / vehiclerental / gen23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -683,7 +683,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / bank / gen2</t>
+          <t>gpt_5_2 / simple / addressbook / gen22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -693,7 +693,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / pickupnet / gen23</t>
+          <t>gpt_4o / simple / restaurant / gen16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -703,7 +703,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / videoclub / gen6 / complex</t>
+          <t>gpt_4o / cot / videoclub / gen6 / boundary</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -713,7 +713,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / addressbook / gen21</t>
+          <t>gpt_5_2 / simple / addressbook / gen18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -723,7 +723,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / myexpenses / gen5</t>
+          <t>gpt_4o / simple / myexpenses / gen7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -733,7 +733,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / myexpenses / gen1 / boundary</t>
+          <t>gpt_4o / cot / restaurant / gen2 / baseline</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -753,7 +753,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / myexpenses / gen27</t>
+          <t>gpt_5_2 / simple / myexpenses / gen17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -763,7 +763,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / statemachine / gen25</t>
+          <t>gpt_4o / simple / restaurant / gen20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -773,7 +773,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / football / gen5 / baseline</t>
+          <t>gpt_4o / cot / football / gen6 / complex</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -783,7 +783,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / addressbook / gen2 / complex</t>
+          <t>gpt_5_2 / cot / bank / gen3 / baseline</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -793,7 +793,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / videoclub / gen1</t>
+          <t>gpt_4o / simple / vehiclerental / gen26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -803,7 +803,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / myexpenses / gen3</t>
+          <t>gpt_4o / simple / hotelmanagement / gen27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -813,7 +813,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / restaurant / gen3 / complex</t>
+          <t>gpt_5_2 / cot / videoclub / gen1 / baseline</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -823,7 +823,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / videoclub / gen2 / boundary</t>
+          <t>gpt_5_2 / cot / statemachine / gen6 / invalid</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -833,7 +833,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / pickupnet / gen10</t>
+          <t>gpt_4o / simple / pickupnet / gen28</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -843,7 +843,7 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / football / gen6 / baseline</t>
+          <t>gpt_4o / cot / hotelmanagement / gen1 / edge</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -930,7 +930,7 @@
             <t xml:space="preserve">0. </t>
           </r>
           <r>
-            <t>Review the following prompts to understand the criteria used during realism evaluation.</t>
+            <t>Review the judge prompts to understand the criteria used during realism evaluation.</t>
           </r>
         </is>
       </c>
@@ -939,7 +939,7 @@
       <c r="A3" s="2" t="inlineStr">
         <is>
           <r>
-            <t>System Judge: https://a-coman.github.io/llm-viewer/gpt_4o/bank/gen1/?view=system-judge-prompt</t>
+            <t>Judge System Prompt: https://a-coman.github.io/llm-viewer/gpt_4o/bank/gen1/?view=system-judge-prompt</t>
           </r>
         </is>
       </c>
@@ -948,7 +948,7 @@
       <c r="A4" s="2" t="inlineStr">
         <is>
           <r>
-            <t>User Judge: https://a-coman.github.io/llm-viewer/gpt_4o/bank/gen1/?view=user-judge-prompt</t>
+            <t>Judge User Prompt: https://a-coman.github.io/llm-viewer/gpt_4o/bank/gen1/?view=user-judge-prompt</t>
           </r>
         </is>
       </c>
@@ -1077,7 +1077,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / vehiclerental / gen12</t>
+          <t>gpt_5_2 / simple / vehiclerental / gen20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -1087,7 +1087,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / videoclub / gen6 / boundary</t>
+          <t>gpt_4o / cot / videoclub / gen5 / complex</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -1097,7 +1097,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / hotelmanagement / gen1</t>
+          <t>gpt_4o / simple / addressbook / gen28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -1107,7 +1107,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / myexpenses / gen16</t>
+          <t>gpt_4o / simple / myexpenses / gen30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -1117,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / vehiclerental / gen20</t>
+          <t>gpt_4o / simple / vehiclerental / gen18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -1127,7 +1127,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / videoclub / gen18</t>
+          <t>gpt_4o / simple / videoclub / gen30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -1137,7 +1137,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / vehiclerental / gen3 / complex</t>
+          <t>gpt_4o / cot / vehiclerental / gen3 / invalid</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1147,7 +1147,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / restaurant / gen25</t>
+          <t>gpt_5_2 / simple / statemachine / gen25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1167,7 +1167,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / restaurant / gen4 / invalid</t>
+          <t>gpt_4o / cot / myexpenses / gen2 / complex</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1177,7 +1177,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / myexpenses / gen3 / complex</t>
+          <t>gpt_5_2 / cot / hotelmanagement / gen2 / baseline</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / statemachine / gen7</t>
+          <t>gpt_4o / simple / restaurant / gen11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / hotelmanagement / gen2 / baseline</t>
+          <t>gpt_5_2 / cot / football / gen3 / invalid</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1217,7 +1217,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / videoclub / gen2 / edge</t>
+          <t>gpt_5_2 / cot / vehiclerental / gen5 / invalid</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1227,7 +1227,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / bank / gen24</t>
+          <t>gpt_5_2 / simple / pickupnet / gen16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1237,7 +1237,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / statemachine / gen20</t>
+          <t>gpt_5_2 / simple / vehiclerental / gen14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1247,7 +1247,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / statemachine / gen27</t>
+          <t>gpt_4o / simple / vehiclerental / gen1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1257,7 +1257,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / statemachine / gen18</t>
+          <t>gpt_5_2 / simple / vehiclerental / gen8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1267,7 +1267,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / videoclub / gen15</t>
+          <t>gpt_4o / simple / videoclub / gen11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1277,7 +1277,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / vehiclerental / gen12</t>
+          <t>gpt_4o / simple / vehiclerental / gen6</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1287,7 +1287,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / addressbook / gen29</t>
+          <t>gpt_5_2 / simple / addressbook / gen19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1297,7 +1297,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / pickupnet / gen22</t>
+          <t>gpt_5_2 / simple / restaurant / gen20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1307,7 +1307,7 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / statemachine / gen1 / edge</t>
+          <t>gpt_4o / cot / restaurant / gen4 / invalid</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1394,7 +1394,7 @@
             <t xml:space="preserve">0. </t>
           </r>
           <r>
-            <t>Review the following prompts to understand the criteria used during realism evaluation.</t>
+            <t>Review the judge prompts to understand the criteria used during realism evaluation.</t>
           </r>
         </is>
       </c>
@@ -1403,7 +1403,7 @@
       <c r="A3" s="2" t="inlineStr">
         <is>
           <r>
-            <t>System Judge: https://a-coman.github.io/llm-viewer/gpt_4o/bank/gen1/?view=system-judge-prompt</t>
+            <t>Judge System Prompt: https://a-coman.github.io/llm-viewer/gpt_4o/bank/gen1/?view=system-judge-prompt</t>
           </r>
         </is>
       </c>
@@ -1412,7 +1412,7 @@
       <c r="A4" s="2" t="inlineStr">
         <is>
           <r>
-            <t>User Judge: https://a-coman.github.io/llm-viewer/gpt_4o/bank/gen1/?view=user-judge-prompt</t>
+            <t>Judge User Prompt: https://a-coman.github.io/llm-viewer/gpt_4o/bank/gen1/?view=user-judge-prompt</t>
           </r>
         </is>
       </c>
@@ -1541,7 +1541,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / statemachine / gen3 / complex</t>
+          <t>gpt_5_2 / cot / videoclub / gen1 / boundary</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -1551,7 +1551,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / vehiclerental / gen2 / complex</t>
+          <t>gpt_5_2 / cot / restaurant / gen4 / edge</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -1561,7 +1561,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / vehiclerental / gen1 / baseline</t>
+          <t>gpt_5_2 / cot / videoclub / gen3 / boundary</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -1571,7 +1571,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / vehiclerental / gen3 / invalid</t>
+          <t>gpt_4o / cot / vehiclerental / gen5 / invalid</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -1581,7 +1581,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / hotelmanagement / gen27</t>
+          <t>gpt_5_2 / simple / pickupnet / gen25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -1591,7 +1591,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / addressbook / gen6 / edge</t>
+          <t>gpt_5_2 / cot / bank / gen3 / complex</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -1601,7 +1601,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / bank / gen5</t>
+          <t>gpt_5_2 / simple / football / gen23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1621,7 +1621,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / hotelmanagement / gen3 / edge</t>
+          <t>gpt_4o / cot / myexpenses / gen5 / baseline</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1631,7 +1631,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / myexpenses / gen6 / baseline</t>
+          <t>gpt_5_2 / cot / pickupnet / gen1 / edge</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1641,7 +1641,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / bank / gen27</t>
+          <t>gpt_5_2 / simple / pickupnet / gen22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1651,7 +1651,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / hotelmanagement / gen27</t>
+          <t>gpt_4o / simple / hotelmanagement / gen25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1661,7 +1661,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / statemachine / gen3</t>
+          <t>gpt_5_2 / simple / vehiclerental / gen22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1671,7 +1671,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / bank / gen6 / invalid</t>
+          <t>gpt_5_2 / cot / addressbook / gen3 / baseline</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1681,7 +1681,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / pickupnet / gen2 / edge</t>
+          <t>gpt_5_2 / cot / pickupnet / gen2 / invalid</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1691,7 +1691,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / bank / gen3 / invalid</t>
+          <t>gpt_4o / cot / addressbook / gen5 / invalid</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1701,7 +1701,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / pickupnet / gen2 / edge</t>
+          <t>gpt_4o / cot / statemachine / gen1 / complex</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / vehiclerental / gen25</t>
+          <t>gpt_5_2 / simple / vehiclerental / gen27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1721,7 +1721,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / myexpenses / gen1 / invalid</t>
+          <t>gpt_4o / cot / hotelmanagement / gen1 / baseline</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1731,7 +1731,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / pickupnet / gen26</t>
+          <t>gpt_5_2 / simple / statemachine / gen20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1741,7 +1741,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / football / gen6 / invalid</t>
+          <t>gpt_5_2 / cot / football / gen4 / invalid</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1751,7 +1751,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / addressbook / gen8</t>
+          <t>gpt_4o / simple / addressbook / gen15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1761,7 +1761,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / pickupnet / gen6 / edge</t>
+          <t>gpt_5_2 / cot / pickupnet / gen3 / edge</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1771,7 +1771,7 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / myexpenses / gen3 / boundary</t>
+          <t>gpt_4o / cot / restaurant / gen3 / complex</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>

--- a/src/scripts/random_eval_2.xlsx
+++ b/src/scripts/random_eval_2.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,7 @@
             <rPr>
               <b val="1"/>
             </rPr>
-            <t>'U: It is implausible to make an omelet without eggs.'</t>
+            <t>'R: We are no verifying real IBANs/BICs.'</t>
           </r>
         </is>
       </c>
@@ -577,53 +577,58 @@
             <rPr>
               <b val="1"/>
             </rPr>
+            <t>'U: It is implausible to make an omelet without eggs.'</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Another valid example: </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
             <t>'D: The component name is too generic for this context.'</t>
           </r>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-    </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Instance Id</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Lola</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Dominik</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Manuel</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / cot / videoclub / gen6 / invalid</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / addressbook / gen6 / invalid</t>
+          <t>gpt_5_2 / cot / pickupnet / gen6 / complex</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -633,7 +638,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / hotelmanagement / gen4 / edge</t>
+          <t>gpt_4o / cot / videoclub / gen5 / invalid</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -643,7 +648,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / myexpenses / gen20</t>
+          <t>gpt_5_2 / cot / hotelmanagement / gen6 / invalid</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -653,7 +658,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / statemachine / gen6 / invalid</t>
+          <t>gpt_5_2 / simple / pickupnet / gen19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -663,7 +668,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / pickupnet / gen24</t>
+          <t>gpt_4o / cot / hotelmanagement / gen5 / boundary</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -673,7 +678,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / vehiclerental / gen23</t>
+          <t>gpt_5_2 / simple / myexpenses / gen25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -683,7 +688,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / addressbook / gen22</t>
+          <t>gpt_4o / cot / restaurant / gen4 / complex</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -693,7 +698,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / restaurant / gen16</t>
+          <t>gpt_5_2 / simple / hotelmanagement / gen5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -703,7 +708,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / videoclub / gen6 / boundary</t>
+          <t>gpt_5_2 / simple / hotelmanagement / gen9</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -713,7 +718,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / addressbook / gen18</t>
+          <t>gpt_4o / simple / restaurant / gen6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -723,7 +728,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / myexpenses / gen7</t>
+          <t>gpt_5_2 / simple / statemachine / gen21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -733,7 +738,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / restaurant / gen2 / baseline</t>
+          <t>gpt_5_2 / cot / pickupnet / gen2 / edge</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -743,7 +748,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / football / gen2 / invalid</t>
+          <t>gpt_5_2 / simple / bank / gen20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -753,7 +758,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / myexpenses / gen17</t>
+          <t>gpt_4o / simple / vehiclerental / gen17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -763,7 +768,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / restaurant / gen20</t>
+          <t>gpt_4o / cot / vehiclerental / gen6 / complex</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -773,7 +778,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / football / gen6 / complex</t>
+          <t>gpt_4o / cot / statemachine / gen4 / baseline</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -783,7 +788,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / bank / gen3 / baseline</t>
+          <t>gpt_4o / simple / vehiclerental / gen22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -793,7 +798,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / vehiclerental / gen26</t>
+          <t>gpt_4o / cot / restaurant / gen6 / invalid</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -803,7 +808,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / hotelmanagement / gen27</t>
+          <t>gpt_5_2 / simple / restaurant / gen17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -813,47 +818,18 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / videoclub / gen1 / baseline</t>
+          <t>gpt_4o / cot / pickupnet / gen2 / boundary</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / cot / statemachine / gen6 / invalid</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>gpt_4o / simple / pickupnet / gen28</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>gpt_4o / cot / hotelmanagement / gen1 / edge</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A4:D4"/>
@@ -864,30 +840,26 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -899,7 +871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1026,7 +998,7 @@
             <rPr>
               <b val="1"/>
             </rPr>
-            <t>'U: It is implausible to make an omelet without eggs.'</t>
+            <t>'R: We are no verifying real IBANs/BICs.'</t>
           </r>
         </is>
       </c>
@@ -1041,53 +1013,58 @@
             <rPr>
               <b val="1"/>
             </rPr>
+            <t>'U: It is implausible to make an omelet without eggs.'</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Another valid example: </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
             <t>'D: The component name is too generic for this context.'</t>
           </r>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-    </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Instance Id</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Lola</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Manuel</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Dominik</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / simple / vehiclerental / gen20</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / videoclub / gen5 / complex</t>
+          <t>gpt_4o / simple / myexpenses / gen22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -1097,7 +1074,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / addressbook / gen28</t>
+          <t>gpt_5_2 / simple / football / gen5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -1107,7 +1084,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / myexpenses / gen30</t>
+          <t>gpt_5_2 / simple / videoclub / gen23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -1117,7 +1094,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / vehiclerental / gen18</t>
+          <t>gpt_5_2 / cot / bank / gen3 / edge</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -1127,7 +1104,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / videoclub / gen30</t>
+          <t>gpt_5_2 / simple / addressbook / gen9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -1137,7 +1114,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / vehiclerental / gen3 / invalid</t>
+          <t>gpt_4o / simple / videoclub / gen25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1147,7 +1124,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / statemachine / gen25</t>
+          <t>gpt_4o / simple / hotelmanagement / gen18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1157,7 +1134,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / addressbook / gen6</t>
+          <t>gpt_4o / simple / football / gen23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1167,7 +1144,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / myexpenses / gen2 / complex</t>
+          <t>gpt_4o / simple / statemachine / gen16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1177,7 +1154,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / hotelmanagement / gen2 / baseline</t>
+          <t>gpt_5_2 / cot / restaurant / gen3 / boundary</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1187,7 +1164,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / restaurant / gen11</t>
+          <t>gpt_5_2 / cot / statemachine / gen4 / edge</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1197,7 +1174,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / football / gen3 / invalid</t>
+          <t>gpt_5_2 / cot / addressbook / gen2 / edge</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1207,7 +1184,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / football / gen4 / invalid</t>
+          <t>gpt_4o / cot / football / gen6 / boundary</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1217,7 +1194,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / vehiclerental / gen5 / invalid</t>
+          <t>gpt_4o / cot / vehiclerental / gen5 / baseline</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1227,7 +1204,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / pickupnet / gen16</t>
+          <t>gpt_4o / simple / addressbook / gen30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1237,7 +1214,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / vehiclerental / gen14</t>
+          <t>gpt_5_2 / cot / hotelmanagement / gen1 / complex</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1247,7 +1224,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / vehiclerental / gen1</t>
+          <t>gpt_5_2 / simple / bank / gen12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1257,7 +1234,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / vehiclerental / gen8</t>
+          <t>gpt_4o / cot / videoclub / gen2 / invalid</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1267,7 +1244,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / videoclub / gen11</t>
+          <t>gpt_5_2 / simple / football / gen30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1277,47 +1254,18 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / vehiclerental / gen6</t>
+          <t>gpt_5_2 / simple / vehiclerental / gen28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / simple / addressbook / gen19</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / simple / restaurant / gen20</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>gpt_4o / cot / restaurant / gen4 / invalid</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A4:D4"/>
@@ -1328,30 +1276,26 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1363,7 +1307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1490,7 +1434,7 @@
             <rPr>
               <b val="1"/>
             </rPr>
-            <t>'U: It is implausible to make an omelet without eggs.'</t>
+            <t>'R: We are no verifying real IBANs/BICs.'</t>
           </r>
         </is>
       </c>
@@ -1505,53 +1449,58 @@
             <rPr>
               <b val="1"/>
             </rPr>
+            <t>'U: It is implausible to make an omelet without eggs.'</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Another valid example: </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
             <t>'D: The component name is too generic for this context.'</t>
           </r>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-    </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Instance Id</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Dominik</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Manuel</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Lola</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / cot / videoclub / gen1 / boundary</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / restaurant / gen4 / edge</t>
+          <t>gpt_4o / simple / pickupnet / gen28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -1561,7 +1510,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / videoclub / gen3 / boundary</t>
+          <t>gpt_4o / cot / statemachine / gen5 / complex</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -1571,7 +1520,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / vehiclerental / gen5 / invalid</t>
+          <t>gpt_5_2 / simple / myexpenses / gen4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -1581,7 +1530,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / pickupnet / gen25</t>
+          <t>gpt_5_2 / simple / addressbook / gen4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -1591,7 +1540,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / bank / gen3 / complex</t>
+          <t>gpt_5_2 / cot / videoclub / gen5 / invalid</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -1601,7 +1550,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / football / gen23</t>
+          <t>gpt_5_2 / cot / addressbook / gen6 / edge</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1611,7 +1560,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / addressbook / gen2 / boundary</t>
+          <t>gpt_4o / simple / bank / gen8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1621,7 +1570,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / myexpenses / gen5 / baseline</t>
+          <t>gpt_5_2 / cot / vehiclerental / gen3 / edge</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1631,7 +1580,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / pickupnet / gen1 / edge</t>
+          <t>gpt_5_2 / simple / pickupnet / gen25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1641,7 +1590,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / pickupnet / gen22</t>
+          <t>gpt_4o / cot / myexpenses / gen1 / invalid</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1651,7 +1600,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / simple / hotelmanagement / gen25</t>
+          <t>gpt_4o / simple / videoclub / gen6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1661,7 +1610,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / vehiclerental / gen22</t>
+          <t>gpt_5_2 / cot / football / gen6 / baseline</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1671,7 +1620,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / addressbook / gen3 / baseline</t>
+          <t>gpt_4o / cot / addressbook / gen2 / invalid</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1681,7 +1630,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / pickupnet / gen2 / invalid</t>
+          <t>gpt_4o / simple / restaurant / gen21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1691,7 +1640,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / addressbook / gen5 / invalid</t>
+          <t>gpt_4o / cot / bank / gen5 / baseline</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1701,7 +1650,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / statemachine / gen1 / complex</t>
+          <t>gpt_5_2 / cot / myexpenses / gen5 / baseline</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1711,7 +1660,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / vehiclerental / gen27</t>
+          <t>gpt_5_2 / cot / football / gen6 / invalid</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1721,7 +1670,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>gpt_4o / cot / hotelmanagement / gen1 / baseline</t>
+          <t>gpt_5_2 / cot / bank / gen4 / complex</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1731,7 +1680,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / simple / statemachine / gen20</t>
+          <t>gpt_4o / simple / statemachine / gen19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1741,47 +1690,18 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>gpt_5_2 / cot / football / gen4 / invalid</t>
+          <t>gpt_5_2 / cot / myexpenses / gen3 / invalid</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>gpt_4o / simple / addressbook / gen15</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>gpt_5_2 / cot / pickupnet / gen3 / edge</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>gpt_4o / cot / restaurant / gen3 / complex</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A4:D4"/>
@@ -1792,30 +1712,26 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/scripts/random_eval_2.xlsx
+++ b/src/scripts/random_eval_2.xlsx
@@ -556,7 +556,7 @@
             <t xml:space="preserve">3. </t>
           </r>
           <r>
-            <t xml:space="preserve">Add a short explanation only for U or D, for example: </t>
+            <t xml:space="preserve">Add a short explanation, for example: </t>
           </r>
           <r>
             <rPr>
@@ -992,7 +992,7 @@
             <t xml:space="preserve">3. </t>
           </r>
           <r>
-            <t xml:space="preserve">Add a short explanation only for U or D, for example: </t>
+            <t xml:space="preserve">Add a short explanation, for example: </t>
           </r>
           <r>
             <rPr>
@@ -1428,7 +1428,7 @@
             <t xml:space="preserve">3. </t>
           </r>
           <r>
-            <t xml:space="preserve">Add a short explanation only for U or D, for example: </t>
+            <t xml:space="preserve">Add a short explanation, for example: </t>
           </r>
           <r>
             <rPr>

--- a/src/scripts/random_eval_2.xlsx
+++ b/src/scripts/random_eval_2.xlsx
@@ -435,13 +435,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="64" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -602,6 +603,7 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -622,6 +624,11 @@
       <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Manuel</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro</t>
         </is>
       </c>
     </row>
@@ -634,6 +641,11 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>R: The object model is syntactically correct and semantically logical. Drivers, customers, and shipments are properly grouped by their respective geographical stations (Dubai and Kigali). The given geolocations correspond accurately to real-world coordinates for those cities. Furthermore, logistics logic is preserved: shipments with the "NEW" status have no driver assigned, while those in progress or delivered have corresponding drivers, and pickup and delivery addresses are distinct.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -644,6 +656,11 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>R: The object model represents a standard, plausible scenario in a video club. A client rents two cassettes (a movie and a series), both of which have logically plausible attributes. The 'availableCopies' being 0 makes sense as they might be currently rented out. Actor and date assignments align realistically with real-world domains.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -654,6 +671,11 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>U: The object 'RM990' of class 'Room' has its 'numBeds' attribute set to 0. This explicitly violates the domain model's logical constraint 'positiveNumBeds' (self.numBeds &gt; 0), creating a contradiction within the given domain model.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -664,6 +686,11 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>U: The shipment 'shp_90002' has its status set to 'ASSIGNED', indicating it has been dispatched or allocated, but it is not linked to any 'Driver' instance via the 'DriverShipment' association. This contradicts the real-world semantic meaning of the status.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -674,6 +701,11 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>U: The bill 'bill43' has a price of 0.0 despite being associated with 'roomReservation21', which contains an extra ('extra21_2' - Coffee and Snacks) that costs 15.0. Additionally, 'room21_701' has a base 'pricePerNight' of 0.0, which is not commercially viable, and renting a projector ('extra21_1') for a standard 1-bed hotel room is logically out of place.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -684,6 +716,11 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>U: The bill `billParkingRefundProcessed_2026_04_06` represents a refund transaction but is assigned a positive amount (6.00). As a result, it is added to the total `Expense` sum (yielding 984.00), effectively increasing the overall cost of the trip instead of decreasing it. This contradicts fundamental real-world accounting logic.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -694,6 +731,11 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>R: The object model represents a plausible real-world restaurant scenario. The property values (prep times, table capacities, dates) are logical and physically possible. The relationship linkages properly map to real-world operations, such as assigning a sufficient number of table seats for reservations, appropriate ingredient units of measure, and correct ownership share distribution (summing to 100).</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -704,6 +746,11 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>U: The booking 'booking7' is simultaneously set to `canceled := true` and `confirmed := true`, which represents a contradictory state. Furthermore, the single booking requires the customer to switch to completely different rooms with fluctuating total bed capacities (4 beds on night 1, 2 beds on night 2, 3 beds on night 3) every single day of a 3-night stay, which is highly impractical and illogical for a real-world hotel visit.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -714,6 +761,11 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>R: The object model represents a highly plausible and logically consistent hotel booking scenario. The dates for the individual room reservations seamlessly cover the entire duration of the main booking. Furthermore, the calculated prices perfectly match the bill amounts (e.g., 'bill16' is 445, which exactly equals 2 nights in 'room430' at 205/night plus a 35 'extraSnackTray'). Extra items and capacities represent common real-world hotel services.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -724,6 +776,11 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>U: The 'FoodItem' object 'foodItem6', which represents 'Prime Beef' (a raw cut of meat purchased by the pound), is associated with the allergen 'Lactose'. Beef does not naturally contain lactose, as it is a sugar exclusively found in dairy products.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -734,6 +791,11 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>R: The object model correctly represents two well-structured state machines for smart grid trading and customer chat operations. The defined states, transitions, source-target topologies, and positive timeout values for events accurately reflect plausible real-world workflows and delays for these domains. All constraints, like positive timer values and lowercase naming conventions, are respected.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -744,6 +806,11 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>U: The addresses and geolocations provided are classic software testing edge cases (e.g., North Pole at 90.0 latitude, South Pole at -90.0, and "Null Island" at 0.0, 0.0 which represents a geocoding error). Orchestrating a physical shipment (SHPEDGE1002) from the North Pole (A100) to the South Pole (A101), or delivering to fictitious buoys, is completely absurd for a real-world commercial logistics network.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -754,6 +821,11 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>U: A 12-year-old Moroccan child ('n6', Ines ElAmrani) is listed as an authorized user for a Chilean joint bank account ('clAcc1') owned by two unrelated Chilean adults ('n4' and 'n5'). While she realistically uses her likely parents' account ('maAcc1'), a minor being an authorized user on a completely unrelated, foreign account is highly implausible in the real world.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -764,6 +836,11 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>U: The object 'truck34' is instantiated as a 'Truck' and given engine-related attributes like a 'gasTankCapacity' of 33.5, an 'odometerReading', and 'mileage', but its 'vehicleTypeCode' is set to '#OPEN_TRAILER'. In reality, an open trailer is unpowered and does not have a gas tank, odometer, or radio.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -774,6 +851,11 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>R: The object model represents a plausible real-world scenario. All variable assignments such as dates, odometer readings, gas tank capacities, and pricing are logically consistent and physically possible. The relationships correctly map vehicles to valid customers and rental agreements, and there are no overlapping dates or contradictory states (e.g., rentals occur before registration expiration dates and after maintenance dates).</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -784,6 +866,11 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>R: The object model represents a highly logical and typical state machine for a industrial conveyor belt. The states ('idle', 'loading', 'moving', 'unloading') represent a valid physical lifecycle, the transitions between them flow sequentially or handle plausible edge cases (moving back to loading), and the time event triggers strictly use biologically and logically sound positive integer values.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -794,6 +881,11 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>U: The object 'truck44' has a 'vehicleTypeCode' of '#COVERED_TRAILER' but is instantiated as a 'Truck' with motorized attributes, including a 'gasTankCapacity' of 28.0 and a 'mileage' of 21. A trailer is an unpowered vehicle and would not have a gas tank, engine mileage, or a standalone odometer/radio.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -804,6 +896,11 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>U: The total capacity of the tables assigned to 'banquet18' (20 + 25 + 30 + 15 = 90) is less than the number of people attending the banquet (100). This violates physical constraints and the 'TablesCapacityGreaterThanPeople' OCL rule.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -814,6 +911,11 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>R: The object model is highly coherent and aligns perfectly with real-world restaurant operations. The values assigned are plausible (e.g., practical preparation times, logical allergen mappings like gluten to puff pastry and seafood to octopus, realistic chronological pacing between reservation times and order times, and appropriate combinations of ingredients for the menu items). All required constraints (like table capacity exceeding party size and owner shares summing to 100) are met.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -824,18 +926,23 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>U: Shipment 'shipment19' has a pickup address in Paris, France ('address39') and a delivery address in Washington, DC, USA ('address40'). It is physically impossible for a single terrestrial 'Driver' ('driver18') to drive a shipment across the Atlantic Ocean. Additionally, a single 'Station' ('station14') directly managing local addresses in London, Paris, and Washington DC contradicts the geographic constraints of a realistic local logistics network.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
@@ -871,13 +978,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="64" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1038,6 +1146,7 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1058,6 +1167,11 @@
       <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Dominik</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro</t>
         </is>
       </c>
     </row>
@@ -1070,6 +1184,11 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>R: The expense amounts of the bills sum up correctly to the total expense amount (7500.00). The bill dates fall logically within the expense's start and end dates. The currency, payment methods, bill statuses, and categories represent a coherent and plausible real-world scenario of office refurbishment.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1080,6 +1199,11 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>U: The object model schedules an official competitive cup match (`matchSDC_1` in the "Spring Derby Cup") between 'teamEA_W' (explicitly named "Eastvale Athletic Women", populated by female players like Sofia Lindgren) and 'teamSF1' ("Stoneford First Team", populated by male players like Nathan Briggs). In real-world football, men's and women's teams do not compete against each other in official formal competitions.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1090,6 +1214,11 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>U: It is highly implausible for a single actor ('na_common') to star in all six completely unrelated media items, which span wildly different formats and genres (a jazz music session, a photography tutorial, a marine biology documentary, an action movie, a comedy movie, and a medical series). This represents an artificial data generation pattern rather than a realistic scenario.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1100,6 +1229,11 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>U: Account 'a46' has a balance of exactly 2,147,483,647 (the maximum value for a 32-bit signed integer), which is an artificial boundary-test value rather than a naturally occurring real-world bank balance. Furthermore, person 'p79' is 2 years old but is assigned as a "user" of account 'a45', which is practically impossible as an infant cannot independently operate a bank account.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1110,6 +1244,11 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>U: The relationship `relBrightHomeCoworkerBank` assigns a `COWORKER` status between two `Company` objects (`brightHomeRepairs` and `civicBank`), which is nonsensical since organizations cannot be coworkers. Additionally, the individuals `taraQuinn` and `svenLarsson` are marked as coworkers despite being employed by completely different companies in different industries.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1120,6 +1259,11 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>R: The object model represents a plausible real-world scenario for a video club. Attribute values such as positive identifiers, realistic dates, valid movie/series titles, and actor names are logically sound. The relationships representing clients having rentals, rentals containing cassettes, and actors acting in specific media all mirror normal video rental operations. A suspended client having a rental is also realistic, as it can represent an overdue past rental that caused the suspension.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1130,6 +1274,11 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>R: The object model represents a plausible hotel booking scenario. The dates for check-in and check-out are valid and align between the booking and reservation. The customer details, room attributes (2 beds, $140/night), standard hotel extras (gym, dinner), and the generated bill ($720) realistically reflect a typical five-night stay.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1140,6 +1289,11 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>R: The object model perfectly aligns with the real-world domain of football. The match scores match the number of goal events exactly (5 total goals), match event times (up to 115) fit within the stated 120-minute match duration (typical for a cup match with extra time), and attributes such as player ages, positions, and ratings are logically consistent and physically plausible.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1150,6 +1304,11 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>R: The object model represents a logical and cyclical cooking process state machine. The flow of states ('ingredientPreparation' -&gt; 'cooking' -&gt; 'plating' -&gt; 'cleaningUp') and transition triggers make sense for a continuous kitchen operation. The time values applied to the events are positive integers, which physically makes sense (e.g., minutes per task), and all constraints are respected.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1160,6 +1319,11 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>R: The object model represents a highly plausible real-world scenario of a large banquet. The numbers align perfectly: exactly 20 tables of 10 capacity for a 200-person reservation, and 5 bus drivers assigned to transport them (~40 passengers per bus). Owner shares correctly sum to 100% per restaurant, and the staff's ages, experience levels, and preparation times for dishes are all completely logical.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1170,6 +1334,11 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>R: The object model represents a valid state machine with an internally consistent "funnel" topology, where multiple specific states logically transition into a single 'silence' sink state. The use of international characters for state names and positive delay values for time events are perfectly plausible in software engineering contexts.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1180,6 +1349,14 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>U: - The object `Note_Cher_1` uses the date '1900-02-29', which is an invalid calendar date because 1900 was not a leap year.
+- `Note_SahelEnergy_1` logs a meeting for a modern "Community solar" company (`C_SahelEnergy_1`) in the year 1582, which is highly anachronistic.
+- The `Company` object `C_MizuhoTemp_1` has an `#EMPLOYEE` relationship to another company (`C_PopupHub_1`). A corporate entity cannot be an employee. 
+- Persons (`P_Cher_1`, `P_OlegPetrov_1`) have `#COWORKER` relationships directed at a `Company`. A person can be a coworker to another person, but not to an entire corporate entity.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1190,6 +1367,11 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>R: The object model accurately represents a football domain scenario. The clubs, teams, and players have logically consistent attributes (e.g., realistic phone numbers and names matching their themes). The match reports correctly align with the match events, as the total score exactly matches the number of 'GOAL' events recorded in both matches. Constraints are respected and relationships are well-formed.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -1200,6 +1382,11 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>U: The object 'truck009' has an `odometerReading` (25000) that is significantly lower than its total `mileage` (40000), which represents a physical contradiction for a vehicle. Additionally, 'rentalAgreement5005' begins on '2024-03-03', but it rents 'truck009' whose `expirationDate` has already passed ('2024-02-09'), making it legally implausible for a professional company to rent out an expired vehicle.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -1210,6 +1397,11 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>U: The relationship 'relationship58' between 'company30' and 'person56' is defined with the type `#SUBDIVISION`. Semantically, a person (Sophia Grant, an Architect) is an individual and cannot be a structural subdivision of a company. The `#EMPLOYEE` relationship type would be the realistic choice here.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -1220,6 +1412,11 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>R: The object model is logically consistent with real-world hotel operations. The dates align correctly within the main booking, and the room attributes, extras (e.g., free baby crib), and prices are completely plausible. Notably, the simulated `Bill` prices meticulously match the exact mathematical calculation of the nightly room rates multiplied by the duration of the reservations, plus the costs of the associated room extras.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -1230,6 +1427,11 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>R: The object model displays strong semantic consistency. Bank details and account identifiers logically match their corresponding countries (Denmark and Brazil). Family names correctly link minors to adult owners, and the model perfectly respects the real-world logic that minors (ages 15 and 17) can be authorized users of an account while ownership is strictly restricted to adults. Balances and joint-account limits (maximum 2 owners) are fully respected.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -1240,6 +1442,11 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>U: The object 'actor25' of class 'Actor' has the name 'N/A', which is a placeholder and not a plausible real-world name for a human being. Additionally, assigning this same placeholder actor to a diverse set of movies and series indicates anomalous data entry.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -1250,6 +1457,11 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>R: The object model accurately reflects a football domain. Player ages, match durations (90 mins), scores, and event timings are all within normal real-world limits. The match events chronologically make sense (e.g., training dates preceding match dates), and the total number of 'GOAL' events perfectly matches the sum of the match scores for both matches, satisfying domain constraints.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -1260,18 +1472,23 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>U: Rental agreement 'ra_150002' represents a trip originating at the Jacksonville, FL office and dropping off at the Flagstaff, AZ office (a distance of approximately 1,900 miles) with an 'anticipatedDuration' of 1 day. It is physically impossible to drive a rental truck that distance in 24 hours.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
@@ -1307,13 +1524,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="64" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1474,6 +1692,7 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1494,6 +1713,11 @@
       <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Lola</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro</t>
         </is>
       </c>
     </row>
@@ -1506,6 +1730,11 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>U: The object 'shipment56' has its status set to '#UNDERWAY' (in transit), but it has no driver assigned to it via the 'DriverShipment' association. In a real-world logistics scenario, a shipment cannot physically be underway without an assigned driver (especially since 'shipment55', which is only '#ASSIGNED', already has one).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1516,6 +1745,11 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>U: The state 'red' has multiple outgoing time-based transitions. Because 'redToPedestrian' and 'anyToEmergency' both have TimeEvents of 1, the machine will always exit the 'red' state after 1 time unit. This makes the 'redToGreen' (60) and 'normalToNight' (420) transitions permanently unreachable, resulting in a logically broken traffic light that never turns green. Additionally, 'anyToEmergency' only originates from 'red', contradicting its name.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1526,6 +1760,11 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>R: The object model represents a plausible real-world scenario where a monthly expense report is created as a placeholder with a total amount of 0.00 and no bills attached yet. The descriptive comments logically explain this state, and the constraint where the expense amount equals the sum of its bills is maintained (0 = 0).</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1536,6 +1775,11 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>R: The object model is syntactically correct and semantically logical. The instantiation carefully aligns with real-world scenarios: valid phone and email structures, logical academic roles (Professor, Postdoc, Grad Student) properly linked to a department, and coherent professional interactions documented in the nested notes. Furthermore, the constraint preventing a contact from having a relationship with themselves is respected.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1546,6 +1790,11 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>U: The rental object 'rentalRioR40' is simultaneously associated with two different clients ('clientRioC40' and 'clientRioC41') in the 'ClientRental' association. This contradicts the domain model's cardinality constraint, which strictly dictates that a rental must be assigned to exactly one client (`Client [1]`).</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1556,6 +1805,11 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>R: The object model represents a newly created, empty AddressBook. This is perfectly realistic, as an address book contains zero contacts when it is first initialized or purchased.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1566,6 +1820,11 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>U: The objects 'account22' and 'account24' have IBANs containing the bank identifier 'ABNA' (ABN AMRO), but they are associated with 'bank15', which represents 'ING Bank'. In the real world, an IBAN strictly corresponds to its issuing bank, making this a logical contradiction.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1576,6 +1835,15 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>U: The object model contains several logically impossible and practically absurd administrative values:
+- `Individual` 'I20' and `Company` 'C20' have negative identification numbers (`driverLicenseNumber` = -12345 and `idNumber` = -999).
+- `RentalAgreement` 'RA301' has an impossible `anticipatedDuration` of 999999, which equates to thousands of years.
+- `RentalAgreement` 'RA303' demands an exorbitant `depositPaid` of 100,000,000.0 (100 million) for a simple truck rental.
+- The single truck 'V200' is simultaneously attached to three overlapping rental agreements ('RA300', 'RA301', 'RA304') starting on the exact same date.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1586,6 +1854,11 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>R: The object model perfectly aligns with the domain constraints and represents a logically consistent real-world logistics scenario. Geolocation coordinates correspond correctly to the assigned German cities, the relationship multiplicities are respected, and the shipment assignment and statuses (e.g., 'NEW' lacking a driver while 'ASSIGNED' having one) reflect plausible business rules. Pickup and delivery addresses are distinct for every shipment as required.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1596,6 +1869,11 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>U: The total amount of the 'vacayTripExpense' is calculated by directly adding 500.00 MAD (Moroccan Dirham) and 700.00 EUR (Euro) to get 1200.00. Semantically, summing raw amounts of different currencies without applying exchange rates makes no real-world financial sense.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1606,6 +1884,11 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>R: The client IDs, movie titles, actor names, and rental dates all represent valid and plausible real-world values. The number of available copies and episode numbers are reasonable positive integers. The relationships appropriately map clients to rentals, rentals to media, and actors to their respective movies or series. Presenting a suspended client with a rental is also realistic, as it likely represents rental history.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1616,6 +1899,11 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>R: The object model is highly consistent and semantically plausible. Attributes such as match scores directly match individual player goals and MatchEvent goal records. The sequence of dates, age ranges, match durations (60 mins for an indoor cup), round-robin format, and diverse geographical profiles of clubs and their players are all logically sound and align perfectly with real-world scenarios.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1626,6 +1914,11 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>R: The object model constructs a highly plausible address book of international NGOs. The attributes are semantically accurate; notably, the international phone codes (+1, +61, +49, +91, +34) perfectly match their respective real-world cities. Applying relationship types like 'BOSS', 'SUBDIVISION', and 'COWORKER' to organizations logically maps to parent companies, branches, and partner agencies, working well within the constraints of the domain model enum.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -1636,6 +1929,11 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>R: All object attributes contain plausible real-world values (e.g., ages, table capacities, preparation times), and the relationships logically model a restaurant's operations. The combined capacities of assigned tables accommodate the reservations, the owner shares sum properly to 100%, and the timing of orders aligns realistically with the reservation times.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -1646,6 +1944,11 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>R: The object model represents a highly plausible banking scenario. The bank, persons, and account details use valid and coherent data (e.g., ages are all over 18, balances are positive, names and BIC codes match the Indian bank context). The relationships properly reflect constraints, such as accounts having exactly one or two owners, and realistic usage delegation (people using accounts they do not exclusively own).</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -1656,6 +1959,11 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>U: The total amount for 'expenseEXP2026073' (5328.90) is calculated by directly summing the raw numerical amounts of its bills, despite them being in different currencies (PHP and SGD). Mathematically adding 18.40 SGD to PHP amounts without applying an exchange rate produces a meaningless real-world financial total.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -1666,6 +1974,11 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>U: The player 'P193' is assigned 4 distinct positions ('POS296', 'POS297', 'POS298', 'POS299'). This violates the domain model's maximum multiplicity of 3 positions per player. Furthermore, it is highly unrealistic in real-world football for a single player to be officially specialized in every possible role on the pitch (Goalkeeper, Defender, Midfielder, and Forward) simultaneously.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -1676,6 +1989,11 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>R: The object model perfectly aligns with reality. Account balances are positive, IBANs match the country context representing each bank, all owners are adults (satisfying the age constraint), and minors simply have "Use" access to older relatives' accounts (e.g., 17-year-old Daan using 56-year-old Jeroen's account), which models real-world family banking.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -1686,6 +2004,11 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>U: The transition 'confirmDelivery' ('transition69') links the source state 'delivered' back to the target state 'orderReceived'. Confirming a delivery should conclude the lifecycle of a parcel, not restart the entire ordering and shipping process in a cyclical loop.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -1696,18 +2019,23 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>R: The objects, attributes, and relationships perfectly represent a realistic business expense scenario. The amounts are computationally consistent (the expense totals exactly match the sums of their associated bills), the dates align logically, and the comments provide plausible real-world context for splitting a shared hotel invoice across two project expenses in Moroccan Dirham.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
